--- a/downloads/arbeitsdateien/07_Schule_2NF_zu_3NF.xlsx
+++ b/downloads/arbeitsdateien/07_Schule_2NF_zu_3NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="Rc833b63d602545be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R1d6e514f10734a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="R89e20a495f424674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER" sheetId="1" r:id="Rbbe96196b42b43e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNTERRICHT" sheetId="2" r:id="R230999b4cb7e406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHUELER_UNTERRICHT" sheetId="3" r:id="R8d566d20932542bc"/>
   </x:sheets>
 </x:workbook>
 </file>
